--- a/data/trans_orig/P1423-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1423-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2007</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25982</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32802</t>
+          <t>32028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58311</t>
+          <t>57916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47337</t>
+          <t>47975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75745</t>
+          <t>77500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>668030</t>
+          <t>668265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>683829</t>
+          <t>684401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>630040</t>
+          <t>630435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655549</t>
+          <t>656323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1306618</t>
+          <t>1304863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1335026</t>
+          <t>1334388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41205</t>
+          <t>40848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59859</t>
+          <t>59779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93077</t>
+          <t>93128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84484</t>
+          <t>84004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126189</t>
+          <t>126739</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>920595</t>
+          <t>920952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>943223</t>
+          <t>942963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>875316</t>
+          <t>875265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>908534</t>
+          <t>908614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1804004</t>
+          <t>1803454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1845709</t>
+          <t>1846189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15029</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40158</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68752</t>
+          <t>68800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62982</t>
+          <t>62732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95515</t>
+          <t>96632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644714</t>
+          <t>643782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663480</t>
+          <t>662577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>615089</t>
+          <t>615041</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>643683</t>
+          <t>641524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1266835</t>
+          <t>1265718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1299368</t>
+          <t>1299618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23497</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45593</t>
+          <t>46095</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68098</t>
+          <t>66299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101658</t>
+          <t>103419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96693</t>
+          <t>97327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139394</t>
+          <t>138798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896629</t>
+          <t>896127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918725</t>
+          <t>918848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>936954</t>
+          <t>935193</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>970514</t>
+          <t>972313</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1841440</t>
+          <t>1842036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1884141</t>
+          <t>1883507</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82495</t>
+          <t>82672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121211</t>
+          <t>122507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>226831</t>
+          <t>226997</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288464</t>
+          <t>288276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>324573</t>
+          <t>326547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>398476</t>
+          <t>396959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3155332</t>
+          <t>3154036</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3194048</t>
+          <t>3193871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3090733</t>
+          <t>3090921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3152366</t>
+          <t>3152200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6257265</t>
+          <t>6258782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6331168</t>
+          <t>6329194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2012</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36974</t>
+          <t>37484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74184</t>
+          <t>73577</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110344</t>
+          <t>109406</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96792</t>
+          <t>99110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137688</t>
+          <t>140561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>666495</t>
+          <t>665985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>686298</t>
+          <t>685964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>586706</t>
+          <t>587644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>622866</t>
+          <t>623473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1262831</t>
+          <t>1259958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1303727</t>
+          <t>1301409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>35067</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64146</t>
+          <t>65306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97997</t>
+          <t>96209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139379</t>
+          <t>138678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142097</t>
+          <t>138755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>190438</t>
+          <t>192234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>953801</t>
+          <t>952641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>983600</t>
+          <t>982880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>889594</t>
+          <t>890295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>930976</t>
+          <t>932764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1856483</t>
+          <t>1854687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1904824</t>
+          <t>1908166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>38639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61386</t>
+          <t>61732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97061</t>
+          <t>97077</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84374</t>
+          <t>83979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125041</t>
+          <t>125970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>719863</t>
+          <t>718984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>742555</t>
+          <t>742756</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>680113</t>
+          <t>680097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>715788</t>
+          <t>715442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1409756</t>
+          <t>1408827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1450423</t>
+          <t>1450818</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32450</t>
+          <t>32387</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59683</t>
+          <t>60460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100902</t>
+          <t>100681</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141956</t>
+          <t>144632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141598</t>
+          <t>140167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191710</t>
+          <t>191641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>888056</t>
+          <t>887279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>915289</t>
+          <t>915352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>909945</t>
+          <t>907269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>950999</t>
+          <t>951220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1807930</t>
+          <t>1807999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1858042</t>
+          <t>1859473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119409</t>
+          <t>118968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169596</t>
+          <t>168850</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>364180</t>
+          <t>366728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>441185</t>
+          <t>444837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>504880</t>
+          <t>506773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>599533</t>
+          <t>597587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3257183</t>
+          <t>3257929</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3307370</t>
+          <t>3307811</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3113913</t>
+          <t>3110261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3190918</t>
+          <t>3188370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6382344</t>
+          <t>6384290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6476997</t>
+          <t>6475104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2016</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27898</t>
+          <t>28385</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63621</t>
+          <t>64681</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96758</t>
+          <t>99072</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80440</t>
+          <t>79231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118931</t>
+          <t>117615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>646902</t>
+          <t>646415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>663509</t>
+          <t>663325</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>576081</t>
+          <t>573767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>609218</t>
+          <t>608158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1228708</t>
+          <t>1230024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1267199</t>
+          <t>1268408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>32569</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76382</t>
+          <t>75149</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114221</t>
+          <t>114505</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94348</t>
+          <t>97874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140896</t>
+          <t>138339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>989297</t>
+          <t>989862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008166</t>
+          <t>1008114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>928692</t>
+          <t>928408</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>966531</t>
+          <t>967764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1924448</t>
+          <t>1927005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1970996</t>
+          <t>1967470</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39695</t>
+          <t>39998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55512</t>
+          <t>57321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>90610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82298</t>
+          <t>80626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122024</t>
+          <t>120942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>719857</t>
+          <t>719554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>740717</t>
+          <t>741382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>694943</t>
+          <t>694401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>729499</t>
+          <t>727690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1422539</t>
+          <t>1423621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1462265</t>
+          <t>1463937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30260</t>
+          <t>30343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57629</t>
+          <t>56666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95950</t>
+          <t>93179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139619</t>
+          <t>138725</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132434</t>
+          <t>133302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183885</t>
+          <t>181908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>879938</t>
+          <t>880901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>907307</t>
+          <t>907224</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>904160</t>
+          <t>905054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>947829</t>
+          <t>950600</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1797461</t>
+          <t>1799438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1848912</t>
+          <t>1848044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92138</t>
+          <t>91379</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133487</t>
+          <t>132771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>327383</t>
+          <t>323651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>399455</t>
+          <t>398752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>425952</t>
+          <t>434571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>515234</t>
+          <t>519549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3260863</t>
+          <t>3261579</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3302212</t>
+          <t>3302971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3145087</t>
+          <t>3145790</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3217159</t>
+          <t>3220891</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6423658</t>
+          <t>6419343</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6512940</t>
+          <t>6504321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2023</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36824</t>
+          <t>37901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63249</t>
+          <t>63922</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58242</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89487</t>
+          <t>91040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103660</t>
+          <t>105552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143308</t>
+          <t>144428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>572192</t>
+          <t>571519</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>598617</t>
+          <t>597540</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>635843</t>
+          <t>634290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>667088</t>
+          <t>664686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1217464</t>
+          <t>1216344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1257112</t>
+          <t>1255220</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>20891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64943</t>
+          <t>63437</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93820</t>
+          <t>93972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124986</t>
+          <t>125334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100792</t>
+          <t>104092</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182052</t>
+          <t>183517</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1127921</t>
+          <t>1129427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1169591</t>
+          <t>1171973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>833665</t>
+          <t>833317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>864831</t>
+          <t>864679</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1969464</t>
+          <t>1967999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2050724</t>
+          <t>2047424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>29496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>57975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>43683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132071</t>
+          <t>134457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92606</t>
+          <t>93780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169143</t>
+          <t>168237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>647636</t>
+          <t>646705</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>674277</t>
+          <t>675184</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>801295</t>
+          <t>798909</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>878879</t>
+          <t>889683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1468903</t>
+          <t>1469809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1545440</t>
+          <t>1544266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47771</t>
+          <t>48342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77740</t>
+          <t>78826</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103706</t>
+          <t>105641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150869</t>
+          <t>154053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164760</t>
+          <t>165414</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218213</t>
+          <t>217529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>849091</t>
+          <t>848005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879060</t>
+          <t>878489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>944063</t>
+          <t>940879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>991226</t>
+          <t>989291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1803550</t>
+          <t>1804234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1857003</t>
+          <t>1856349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156248</t>
+          <t>155788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>231927</t>
+          <t>229127</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>333079</t>
+          <t>334413</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>458157</t>
+          <t>455450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>533889</t>
+          <t>525435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>673135</t>
+          <t>669137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3227890</t>
+          <t>3230690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3303569</t>
+          <t>3304029</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3254123</t>
+          <t>3256830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3379201</t>
+          <t>3377867</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6498962</t>
+          <t>6502960</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6638208</t>
+          <t>6646662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1423-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1423-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32028</t>
+          <t>33446</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57916</t>
+          <t>58374</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47975</t>
+          <t>45683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77500</t>
+          <t>77306</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>668265</t>
+          <t>669330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>684401</t>
+          <t>684453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>630435</t>
+          <t>629977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>656323</t>
+          <t>654905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1304863</t>
+          <t>1305057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1334388</t>
+          <t>1336680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40848</t>
+          <t>39578</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59779</t>
+          <t>59734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93128</t>
+          <t>95324</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84004</t>
+          <t>83908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126739</t>
+          <t>122849</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>920952</t>
+          <t>922222</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>942963</t>
+          <t>943030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>875265</t>
+          <t>873069</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>908614</t>
+          <t>908659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1803454</t>
+          <t>1807344</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1846189</t>
+          <t>1846285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>15786</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>35598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>40910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68800</t>
+          <t>67661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62732</t>
+          <t>62642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96632</t>
+          <t>97159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643782</t>
+          <t>642911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662577</t>
+          <t>662723</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>615041</t>
+          <t>616180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641524</t>
+          <t>642931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1265718</t>
+          <t>1265191</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1299618</t>
+          <t>1299708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46095</t>
+          <t>47148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66299</t>
+          <t>66161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103419</t>
+          <t>102143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97327</t>
+          <t>97695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138798</t>
+          <t>139595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896127</t>
+          <t>895074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918848</t>
+          <t>918739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>935193</t>
+          <t>936469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>972313</t>
+          <t>972451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1842036</t>
+          <t>1841239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1883507</t>
+          <t>1883139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82672</t>
+          <t>83266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122507</t>
+          <t>121468</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>226997</t>
+          <t>222029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288276</t>
+          <t>284522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>326547</t>
+          <t>318267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>396959</t>
+          <t>393864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3154036</t>
+          <t>3155075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3193871</t>
+          <t>3193277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3090921</t>
+          <t>3094675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3152200</t>
+          <t>3157168</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6258782</t>
+          <t>6261877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6329194</t>
+          <t>6337474</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37484</t>
+          <t>37399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73577</t>
+          <t>72989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109406</t>
+          <t>107902</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99110</t>
+          <t>96720</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140561</t>
+          <t>137813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665985</t>
+          <t>666070</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>685964</t>
+          <t>686108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>587644</t>
+          <t>589148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>623473</t>
+          <t>624061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1259958</t>
+          <t>1262706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1301409</t>
+          <t>1303799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35067</t>
+          <t>34661</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65306</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96209</t>
+          <t>97008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138678</t>
+          <t>137266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>138755</t>
+          <t>140220</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192234</t>
+          <t>192284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>952641</t>
+          <t>954520</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>982880</t>
+          <t>983286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>890295</t>
+          <t>891707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>932764</t>
+          <t>931965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1854687</t>
+          <t>1854637</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1908166</t>
+          <t>1906701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>15610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38639</t>
+          <t>39246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61732</t>
+          <t>61277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97077</t>
+          <t>96946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83979</t>
+          <t>84349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125970</t>
+          <t>124989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>718984</t>
+          <t>718377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>742756</t>
+          <t>742013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>680097</t>
+          <t>680228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>715442</t>
+          <t>715897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1408827</t>
+          <t>1409808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1450818</t>
+          <t>1450448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32387</t>
+          <t>31483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60460</t>
+          <t>60288</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100681</t>
+          <t>100171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144632</t>
+          <t>140709</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140167</t>
+          <t>140035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191641</t>
+          <t>190926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>887279</t>
+          <t>887451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>915352</t>
+          <t>916256</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>907269</t>
+          <t>911192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>951220</t>
+          <t>951730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1807999</t>
+          <t>1808714</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1859473</t>
+          <t>1859605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118968</t>
+          <t>117403</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168850</t>
+          <t>170544</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>366728</t>
+          <t>371315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>444837</t>
+          <t>444017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>506773</t>
+          <t>504603</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>597587</t>
+          <t>594476</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3257929</t>
+          <t>3256235</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3307811</t>
+          <t>3309376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3110261</t>
+          <t>3111081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3188370</t>
+          <t>3183783</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6384290</t>
+          <t>6387401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6475104</t>
+          <t>6477274</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>28157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64681</t>
+          <t>62667</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99072</t>
+          <t>95418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79231</t>
+          <t>79310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117615</t>
+          <t>117886</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>646415</t>
+          <t>646643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>663325</t>
+          <t>663605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>573767</t>
+          <t>577421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>608158</t>
+          <t>610172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1230024</t>
+          <t>1229753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1268408</t>
+          <t>1268329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32569</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75149</t>
+          <t>75608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114505</t>
+          <t>115318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97874</t>
+          <t>94458</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138339</t>
+          <t>139629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>989862</t>
+          <t>989730</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008114</t>
+          <t>1008076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>928408</t>
+          <t>927595</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>967764</t>
+          <t>967305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1927005</t>
+          <t>1925715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1967470</t>
+          <t>1970886</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>41267</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,82 +5328,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>72276</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>56279</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>90163</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>100032</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>81377</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>120102</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>5,27%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>72276</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>57321</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>90610</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>100032</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>80626</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>120942</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>719554</t>
+          <t>718285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>741382</t>
+          <t>740850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,82 +5441,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>712735</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>694848</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>728732</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>88,51%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1444531</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1424461</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1463186</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>93,52%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>94,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>712735</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>694401</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>727690</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>88,46%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1444531</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1423621</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1463937</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>93,52%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56666</t>
+          <t>55709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93179</t>
+          <t>95180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138725</t>
+          <t>137734</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133302</t>
+          <t>134522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181908</t>
+          <t>184094</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>880901</t>
+          <t>881858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>907224</t>
+          <t>906980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>905054</t>
+          <t>906045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>950600</t>
+          <t>948599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1799438</t>
+          <t>1797252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1848044</t>
+          <t>1846824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91379</t>
+          <t>91904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132771</t>
+          <t>132452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>323651</t>
+          <t>323335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>398752</t>
+          <t>399186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>434571</t>
+          <t>434479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>519549</t>
+          <t>521099</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3261579</t>
+          <t>3261898</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3302971</t>
+          <t>3302446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3145790</t>
+          <t>3145356</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3220891</t>
+          <t>3221207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6419343</t>
+          <t>6417793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6504321</t>
+          <t>6504413</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>52421</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37901</t>
+          <t>40147</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63922</t>
+          <t>68680</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>76039</t>
+          <t>82123</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60644</t>
+          <t>70017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91040</t>
+          <t>97067</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>124739</t>
+          <t>134544</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105552</t>
+          <t>118133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144428</t>
+          <t>157468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>586740</t>
+          <t>638289</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571519</t>
+          <t>622030</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>597540</t>
+          <t>650563</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>649291</t>
+          <t>652057</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>634290</t>
+          <t>637113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664686</t>
+          <t>664163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1236033</t>
+          <t>1290345</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1216344</t>
+          <t>1267421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1255220</t>
+          <t>1306756</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20891</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63437</t>
+          <t>62288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>108805</t>
+          <t>120663</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93972</t>
+          <t>103932</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125334</t>
+          <t>139105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>153461</t>
+          <t>169601</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104092</t>
+          <t>146992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183517</t>
+          <t>190729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1148207</t>
+          <t>999978</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1129427</t>
+          <t>986629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1171973</t>
+          <t>1013544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>849846</t>
+          <t>950811</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>833317</t>
+          <t>932369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>864679</t>
+          <t>967542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1998055</t>
+          <t>1950790</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1967999</t>
+          <t>1929662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2047424</t>
+          <t>1973399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40951</t>
+          <t>44872</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29496</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57975</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>97737</t>
+          <t>111673</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>92520</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134457</t>
+          <t>128057</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>138688</t>
+          <t>156545</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93780</t>
+          <t>134195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168237</t>
+          <t>182964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>663729</t>
+          <t>758201</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>646705</t>
+          <t>741833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675184</t>
+          <t>770926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>835629</t>
+          <t>700586</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>798909</t>
+          <t>684202</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>889683</t>
+          <t>719739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1499358</t>
+          <t>1458787</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1469809</t>
+          <t>1432368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1544266</t>
+          <t>1481137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63059</t>
+          <t>68815</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48342</t>
+          <t>55483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78826</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>130546</t>
+          <t>142172</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105641</t>
+          <t>123247</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>154053</t>
+          <t>163226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>193605</t>
+          <t>210987</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165414</t>
+          <t>185644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217529</t>
+          <t>236948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>863772</t>
+          <t>921247</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>848005</t>
+          <t>902013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878489</t>
+          <t>934579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>964386</t>
+          <t>976869</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>940879</t>
+          <t>955815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>989291</t>
+          <t>995794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1828158</t>
+          <t>1898117</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1804234</t>
+          <t>1872156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1856349</t>
+          <t>1923460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>197367</t>
+          <t>215047</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155788</t>
+          <t>186900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>229127</t>
+          <t>247797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>413127</t>
+          <t>456631</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>334413</t>
+          <t>422986</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>455450</t>
+          <t>493459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>610494</t>
+          <t>671678</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>525435</t>
+          <t>620917</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>669137</t>
+          <t>712908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3262450</t>
+          <t>3317715</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3230690</t>
+          <t>3284965</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3304029</t>
+          <t>3345862</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3299153</t>
+          <t>3280323</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3256830</t>
+          <t>3243495</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3377867</t>
+          <t>3313968</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6561603</t>
+          <t>6598038</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6502960</t>
+          <t>6556808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6646662</t>
+          <t>6648799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
